--- a/cleaning_pipeline_R/dictionaries/dictionary_zim_twenty_8_day_follow_up.xlsx
+++ b/cleaning_pipeline_R/dictionaries/dictionary_zim_twenty_8_day_follow_up.xlsx
@@ -2528,7 +2528,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Outcome</t>
+          <t>Outcome at discharge</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -3380,7 +3380,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F126"/>
+  <dimension ref="A1:F125"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -3813,12 +3813,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>DUM</t>
+          <t>HIVLR</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Abandoned baby</t>
+          <t>HIV low risk</t>
         </is>
       </c>
       <c r="D15">
@@ -3826,12 +3826,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>8be57d79-6bb9-4de8-a3a1-1d699a513f7b</t>
+          <t>243252d5-c833-4428-9ed9-ab7db1af7bc7</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>DUM</t>
+          <t>HIVLR</t>
         </is>
       </c>
     </row>
@@ -3843,12 +3843,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>HIVLR</t>
+          <t>HIVHR</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>HIV low risk</t>
+          <t>HIV high risk</t>
         </is>
       </c>
       <c r="D16">
@@ -3856,12 +3856,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>243252d5-c833-4428-9ed9-ab7db1af7bc7</t>
+          <t>4a447bcc-b8c5-4a7d-8adb-5d8dddf1172c</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>HIVLR</t>
+          <t>HIVHR</t>
         </is>
       </c>
     </row>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>HIVHR</t>
+          <t>HypogAs</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>HIV high risk</t>
+          <t>Hypoglycaemia (NOT symptomatic)</t>
         </is>
       </c>
       <c r="D17">
@@ -3886,12 +3886,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>4a447bcc-b8c5-4a7d-8adb-5d8dddf1172c</t>
+          <t>9295fe69-649f-47b5-ba35-9cb2762bfc77</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>HIVHR</t>
+          <t>HypogAs</t>
         </is>
       </c>
     </row>
@@ -3903,12 +3903,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>HypogAs</t>
+          <t>HypogSy</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Hypoglycaemia (NOT symptomatic)</t>
+          <t>Hypoglycaemia (symptomatic)</t>
         </is>
       </c>
       <c r="D18">
@@ -3916,12 +3916,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>9295fe69-649f-47b5-ba35-9cb2762bfc77</t>
+          <t>7458bc48-1b80-45fc-9c76-8bd0839d6493</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>HypogAs</t>
+          <t>HypogSy</t>
         </is>
       </c>
     </row>
@@ -3933,12 +3933,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>HypogSy</t>
+          <t>HIE</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Hypoglycaemia (Symptomatic)</t>
+          <t>Birth Asphyxia / Hypoxic Ischaemic Encephalopathy (HIE)</t>
         </is>
       </c>
       <c r="D19">
@@ -3946,12 +3946,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>7458bc48-1b80-45fc-9c76-8bd0839d6493</t>
+          <t>159642b1-956f-440b-8006-1e2672565f37</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>HypogSy</t>
+          <t>HIE</t>
         </is>
       </c>
     </row>
@@ -3963,12 +3963,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>HIE</t>
+          <t>GSchis</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Birth Asphyxia/ Hypoxic Ischaemic Encephalopathy (HIE)</t>
+          <t>Gastroschisis</t>
         </is>
       </c>
       <c r="D20">
@@ -3976,12 +3976,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>159642b1-956f-440b-8006-1e2672565f37</t>
+          <t>8c46b45f-ca6f-428a-a990-cd0781f29953</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>HIE</t>
+          <t>GSchis</t>
         </is>
       </c>
     </row>
@@ -3993,12 +3993,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>GSchis</t>
+          <t>MJ</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Gastroschisis</t>
+          <t>Jaundice (physiological)</t>
         </is>
       </c>
       <c r="D21">
@@ -4006,12 +4006,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>8c46b45f-ca6f-428a-a990-cd0781f29953</t>
+          <t>3b00efc1-c61e-4a01-8d50-abfe0630fc7d</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>GSchis</t>
+          <t>MJ</t>
         </is>
       </c>
     </row>
@@ -4023,12 +4023,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>MJ</t>
+          <t>LBW</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Physiological Jaundice</t>
+          <t>Low Birth Weight (1500-2499g)</t>
         </is>
       </c>
       <c r="D22">
@@ -4036,12 +4036,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>3b00efc1-c61e-4a01-8d50-abfe0630fc7d</t>
+          <t>7a25194a-1612-4dfe-bdb0-17f6cb6f7302</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>MJ</t>
+          <t>LBW</t>
         </is>
       </c>
     </row>
@@ -4053,12 +4053,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>LBW</t>
+          <t>VLBW</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Low Birth Weight (1500-2499g)</t>
+          <t>Very Low Birth Weight (1000-1499g)</t>
         </is>
       </c>
       <c r="D23">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>7a25194a-1612-4dfe-bdb0-17f6cb6f7302</t>
+          <t>5ff36144-79aa-4077-b748-9e172152e4ae</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>LBW</t>
+          <t>VLBW</t>
         </is>
       </c>
     </row>
@@ -4083,12 +4083,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>VLBW</t>
+          <t>ExLBW</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Very Low Birth Weight (1000-1499g)</t>
+          <t>ExtremelyLow Birth Weight (&lt;1000g)</t>
         </is>
       </c>
       <c r="D24">
@@ -4096,12 +4096,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>5ff36144-79aa-4077-b748-9e172152e4ae</t>
+          <t>df4cb4a5-f815-409d-8072-327b7b3f0e4c</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>VLBW</t>
+          <t>ExLBW</t>
         </is>
       </c>
     </row>
@@ -4113,12 +4113,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>ExLBW</t>
+          <t>MecEx</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>ExtremelyLow Birth Weight (&lt;1000g)</t>
+          <t>Meconium exposure (not symptomatic)</t>
         </is>
       </c>
       <c r="D25">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>df4cb4a5-f815-409d-8072-327b7b3f0e4c</t>
+          <t>ed9e5d7b-f9b1-4037-a7bf-c53e257700ef</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>ExLBW</t>
+          <t>MecEx</t>
         </is>
       </c>
     </row>
@@ -4143,12 +4143,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>MecEx</t>
+          <t>MiHypo</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Meconium exposure (not symptomatic)</t>
+          <t>Mild Hypothermia</t>
         </is>
       </c>
       <c r="D26">
@@ -4156,12 +4156,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>ed9e5d7b-f9b1-4037-a7bf-c53e257700ef</t>
+          <t>584d8cfd-e44b-4b7d-8b39-31dc05895d28</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>MecEx</t>
+          <t>MiHypo</t>
         </is>
       </c>
     </row>
@@ -4173,12 +4173,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>MiHypo</t>
+          <t>ModHypo</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Mild Hypothermia</t>
+          <t>Moderate Hypothermia</t>
         </is>
       </c>
       <c r="D27">
@@ -4186,12 +4186,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>584d8cfd-e44b-4b7d-8b39-31dc05895d28</t>
+          <t>0319f271-4dca-4aed-aba6-a1a33b56bceb</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>MiHypo</t>
+          <t>ModHypo</t>
         </is>
       </c>
     </row>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ModHypo</t>
+          <t>SHypo</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Moderate Hypothermia</t>
+          <t>Severe Hypothermia</t>
         </is>
       </c>
       <c r="D28">
@@ -4216,12 +4216,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0319f271-4dca-4aed-aba6-a1a33b56bceb</t>
+          <t>e8f09d3e-8959-4dfd-932d-f59a7e7d427b</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>ModHypo</t>
+          <t>SHypo</t>
         </is>
       </c>
     </row>
@@ -4233,12 +4233,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>SHypo</t>
+          <t>Hyperth</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Severe Hypothermia</t>
+          <t>Hyperthermia</t>
         </is>
       </c>
       <c r="D29">
@@ -4246,12 +4246,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>e8f09d3e-8959-4dfd-932d-f59a7e7d427b</t>
+          <t>8d07a953-cd26-4c54-9777-83147f22b500</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>SHypo</t>
+          <t>Hyperth</t>
         </is>
       </c>
     </row>
@@ -4263,12 +4263,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Hyperth</t>
+          <t>SEPS</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Hyperthermia</t>
+          <t>Neonatal Sepsis</t>
         </is>
       </c>
       <c r="D30">
@@ -4276,12 +4276,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>8d07a953-cd26-4c54-9777-83147f22b500</t>
+          <t>daa9886a-6d27-41f8-9fe4-55021a63b18f</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Hyperth</t>
+          <t>SEPS</t>
         </is>
       </c>
     </row>
@@ -4293,12 +4293,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>SEPS</t>
+          <t>Risk</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Neonatal Sepsis</t>
+          <t>Risk factors for sepsis (asymptomatic baby)</t>
         </is>
       </c>
       <c r="D31">
@@ -4306,12 +4306,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>daa9886a-6d27-41f8-9fe4-55021a63b18f</t>
+          <t>36c6d337-0973-4088-bc69-1dd70ba78841</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>SEPS</t>
+          <t>Risk</t>
         </is>
       </c>
     </row>
@@ -4323,12 +4323,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Risk</t>
+          <t>NB</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Risk factors for sepsis (asymptomatic baby)</t>
+          <t>Normal baby</t>
         </is>
       </c>
       <c r="D32">
@@ -4336,12 +4336,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>36c6d337-0973-4088-bc69-1dd70ba78841</t>
+          <t>368afbb3-e9c3-4105-bc68-5307f0abc5e9</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Risk</t>
+          <t>NB</t>
         </is>
       </c>
     </row>
@@ -4353,12 +4353,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>NB</t>
+          <t>PN</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Normal baby</t>
+          <t>Pneumonia / Bronchiolitis</t>
         </is>
       </c>
       <c r="D33">
@@ -4366,12 +4366,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>368afbb3-e9c3-4105-bc68-5307f0abc5e9</t>
+          <t>3b16402d-0c16-4725-92d6-57d3cbc1ab1a</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>NB</t>
+          <t>PN</t>
         </is>
       </c>
     </row>
@@ -4383,12 +4383,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>PN</t>
+          <t>Prem</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Pneumonia / Bronchiolitis</t>
+          <t>Premature (32 to 36.6 weeks)</t>
         </is>
       </c>
       <c r="D34">
@@ -4396,12 +4396,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>3b16402d-0c16-4725-92d6-57d3cbc1ab1a</t>
+          <t>9ffd995c-a13d-4b98-bc3b-e795579b6ee5</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>PN</t>
+          <t>Prem</t>
         </is>
       </c>
     </row>
@@ -4413,12 +4413,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Prem</t>
+          <t>VPrem</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Premature (32 to 36.6 weeks)</t>
+          <t>Very Premature (28 to 31.6 weeks)</t>
         </is>
       </c>
       <c r="D35">
@@ -4426,12 +4426,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>9ffd995c-a13d-4b98-bc3b-e795579b6ee5</t>
+          <t>36b9b7b9-b13a-4d9e-9725-33e7d49309c4</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Prem</t>
+          <t>VPrem</t>
         </is>
       </c>
     </row>
@@ -4443,12 +4443,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>VPrem</t>
+          <t>ExPrem</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Very Premature (28-31 weeks)</t>
+          <t>Extremely Premature (&lt;28 weeks)</t>
         </is>
       </c>
       <c r="D36">
@@ -4456,12 +4456,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>36b9b7b9-b13a-4d9e-9725-33e7d49309c4</t>
+          <t>3e0413a8-4388-49d6-bfda-0e17c5d3d2cb</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>VPrem</t>
+          <t>ExPrem</t>
         </is>
       </c>
     </row>
@@ -4473,12 +4473,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>ExPrem</t>
+          <t>PremRD</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Extremely Premature (&lt;28 weeks)</t>
+          <t>Premature baby with Respiratory Distress</t>
         </is>
       </c>
       <c r="D37">
@@ -4486,12 +4486,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>3e0413a8-4388-49d6-bfda-0e17c5d3d2cb</t>
+          <t>fee9b3a4-d019-45f0-8060-9eb706f2b2a7</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>ExPrem</t>
+          <t>PremRD</t>
         </is>
       </c>
     </row>
@@ -4503,12 +4503,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>PremRD</t>
+          <t>TTN</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Premature baby with Respiratory Distress</t>
+          <t>Transient Tachypnoea of Newborn (TTN)</t>
         </is>
       </c>
       <c r="D38">
@@ -4516,12 +4516,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>fee9b3a4-d019-45f0-8060-9eb706f2b2a7</t>
+          <t>37b883c7-b227-4ede-a9b3-6fcacd0e528b</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>PremRD</t>
+          <t>TTN</t>
         </is>
       </c>
     </row>
@@ -4533,12 +4533,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>TTN</t>
+          <t>Oth</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Transient Tachypnoea of Newborn (TTN)</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D39">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>37b883c7-b227-4ede-a9b3-6fcacd0e528b</t>
+          <t>db05c62c-8ead-4534-812a-777c44f15582</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>TTN</t>
+          <t>Oth</t>
         </is>
       </c>
     </row>
@@ -4563,12 +4563,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Oth</t>
+          <t>TermRD</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Respiratory Distress (term baby)</t>
         </is>
       </c>
       <c r="D40">
@@ -4576,12 +4576,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>db05c62c-8ead-4534-812a-777c44f15582</t>
+          <t>44ac2e73-bc9c-443b-a2f6-e12ac35bf46b</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Oth</t>
+          <t>TermRD</t>
         </is>
       </c>
     </row>
@@ -4593,12 +4593,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>TermRD</t>
+          <t>DJ</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Term with RD</t>
+          <t>Jaundice (pathological)</t>
         </is>
       </c>
       <c r="D41">
@@ -4606,12 +4606,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>44ac2e73-bc9c-443b-a2f6-e12ac35bf46b</t>
+          <t>4f630173-97e1-4698-bf7e-3bfb62ea8b0b</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>TermRD</t>
+          <t>DJ</t>
         </is>
       </c>
     </row>
@@ -4623,12 +4623,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>DJ</t>
+          <t>sHIE</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Pathological Jaundice</t>
+          <t>Suspected Hypoxic Ischaemic Encephalopathy</t>
         </is>
       </c>
       <c r="D42">
@@ -4636,12 +4636,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>4f630173-97e1-4698-bf7e-3bfb62ea8b0b</t>
+          <t>f46a6f89-69e8-4d63-bf17-7cb3cabbbd85</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>DJ</t>
+          <t>sHIE</t>
         </is>
       </c>
     </row>
@@ -4653,12 +4653,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>sHIE</t>
+          <t>ProJ</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Suspected Hypoxic Ischaemic Encephalopathy</t>
+          <t>Jaundice (prolonged)</t>
         </is>
       </c>
       <c r="D43">
@@ -4666,12 +4666,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>f46a6f89-69e8-4d63-bf17-7cb3cabbbd85</t>
+          <t>67db2930-db77-4399-b3f5-58a3a7cd2324</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>sHIE</t>
+          <t>ProJ</t>
         </is>
       </c>
     </row>
@@ -4683,12 +4683,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>PJaundice</t>
+          <t>CleftLip</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Prolonged Jaundice</t>
+          <t>Cleft lip</t>
         </is>
       </c>
       <c r="D44">
@@ -4696,12 +4696,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>67db2930-db77-4399-b3f5-58a3a7cd2324</t>
+          <t>914e3df7-432c-4a57-a27b-9e6b776e5b86</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>PJaundice</t>
+          <t>CleftLip</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>CleftLip</t>
+          <t>CleftRD</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Cleft lip</t>
+          <t>Cleft lip and/or palate with RD</t>
         </is>
       </c>
       <c r="D45">
@@ -4726,12 +4726,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>914e3df7-432c-4a57-a27b-9e6b776e5b86</t>
+          <t>faef241d-0f6e-43a0-a9e4-81fc3b165a05</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>CleftLip</t>
+          <t>CleftRD</t>
         </is>
       </c>
     </row>
@@ -4743,12 +4743,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>CleftRD</t>
+          <t>CleftLipPalate</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Cleft lip and/or palate with RD</t>
+          <t>Cleft lip and/or palate</t>
         </is>
       </c>
       <c r="D46">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>faef241d-0f6e-43a0-a9e4-81fc3b165a05</t>
+          <t>5938dbd6-1a36-467b-b8a6-d449fea26546</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>CleftRD</t>
+          <t>CleftLipPalate</t>
         </is>
       </c>
     </row>
@@ -4773,12 +4773,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>CleftLipPalate</t>
+          <t>Omph</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Cleft lip and/or palate</t>
+          <t>Omphalocele/ Exomphalos</t>
         </is>
       </c>
       <c r="D47">
@@ -4786,12 +4786,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>5938dbd6-1a36-467b-b8a6-d449fea26546</t>
+          <t>5eabb008-c8f6-46fb-a6b2-fce26bd187ed</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>CleftLipPalate</t>
+          <t>Omph</t>
         </is>
       </c>
     </row>
@@ -4803,12 +4803,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Omph</t>
+          <t>Myelo</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Omphalocele/ Exomphalos</t>
+          <t>Myelomeningocele / Spina Bifida</t>
         </is>
       </c>
       <c r="D48">
@@ -4816,12 +4816,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>5eabb008-c8f6-46fb-a6b2-fce26bd187ed</t>
+          <t>60ce8813-1be6-47df-84be-2239c40190ff</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Omph</t>
+          <t>Myelo</t>
         </is>
       </c>
     </row>
@@ -4833,12 +4833,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Myelo</t>
+          <t>CDH</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Myelomeningocele / Spina Bifida</t>
+          <t>Congenital dislocation of the hip (CDH)</t>
         </is>
       </c>
       <c r="D49">
@@ -4846,12 +4846,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>60ce8813-1be6-47df-84be-2239c40190ff</t>
+          <t>c372101d-d0c7-44c1-bb45-4121d77643af</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Myelo</t>
+          <t>CDH</t>
         </is>
       </c>
     </row>
@@ -4863,12 +4863,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>CDH</t>
+          <t>MiTalipes</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Congenital Dislocation of the hip (CDH)</t>
+          <t>Talipes MILD (club foot)</t>
         </is>
       </c>
       <c r="D50">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>c372101d-d0c7-44c1-bb45-4121d77643af</t>
+          <t>e3ae6e68-2aa5-4200-9d5a-738f86d68b9f</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>CDH</t>
+          <t>MiTalipes</t>
         </is>
       </c>
     </row>
@@ -4893,12 +4893,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>MiTalipes</t>
+          <t>MoTalipes</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Mild Talipes (club foot)</t>
+          <t>Moderate Talipes (club foot)</t>
         </is>
       </c>
       <c r="D51">
@@ -4906,12 +4906,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>e3ae6e68-2aa5-4200-9d5a-738f86d68b9f</t>
+          <t>8c78b28d-b053-4841-b756-c207b84e7820</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>MiTalipes</t>
+          <t>MoTalipes</t>
         </is>
       </c>
     </row>
@@ -4923,12 +4923,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>MoTalipes</t>
+          <t>HYDR</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Moderate Talipes (club foot)</t>
+          <t>Hydrocephalus</t>
         </is>
       </c>
       <c r="D52">
@@ -4936,12 +4936,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>8c78b28d-b053-4841-b756-c207b84e7820</t>
+          <t>50d378a8-61e2-49f0-aaf4-90df0e41c965</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>MoTalipes</t>
+          <t>HYDR</t>
         </is>
       </c>
     </row>
@@ -4953,12 +4953,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>HYDR</t>
+          <t>ASP</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Hydrocephalus</t>
+          <t>Aspiration</t>
         </is>
       </c>
       <c r="D53">
@@ -4966,12 +4966,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>50d378a8-61e2-49f0-aaf4-90df0e41c965</t>
+          <t>4b2c7af8-0c85-4ffc-9ef0-6179e5678e57</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>HYDR</t>
+          <t>ASP</t>
         </is>
       </c>
     </row>
@@ -4983,12 +4983,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ASP</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Aspiration</t>
+          <t>Meconium Aspiration</t>
         </is>
       </c>
       <c r="D54">
@@ -4996,12 +4996,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>4b2c7af8-0c85-4ffc-9ef0-6179e5678e57</t>
+          <t>64d41cbd-1af4-409d-aec2-7d8b3bea0a95</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>ASP</t>
+          <t>MA</t>
         </is>
       </c>
     </row>
@@ -5013,12 +5013,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>Gast</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Meconium Aspiration</t>
+          <t>Gastroenteritsis/ Diarrhoea</t>
         </is>
       </c>
       <c r="D55">
@@ -5026,12 +5026,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>64d41cbd-1af4-409d-aec2-7d8b3bea0a95</t>
+          <t>04e7eb7e-35e6-4104-809a-f00509b983d0</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>Gast</t>
         </is>
       </c>
     </row>
@@ -5043,12 +5043,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Gast</t>
+          <t>TOF</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Gastroenteritsis/ Diarrhoea</t>
+          <t>Tracheo-oesophageal fistula</t>
         </is>
       </c>
       <c r="D56">
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>04e7eb7e-35e6-4104-809a-f00509b983d0</t>
+          <t>d515f2c4-d39e-43ab-ba89-b14de9d86e86</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Gast</t>
+          <t>TOF</t>
         </is>
       </c>
     </row>
@@ -5073,12 +5073,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>TOF</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Tracheo-oesophageal fistula</t>
+          <t>Necrotising Enterocolitis (NEC)</t>
         </is>
       </c>
       <c r="D57">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>d515f2c4-d39e-43ab-ba89-b14de9d86e86</t>
+          <t>470b83f0-119e-4d3a-b4ea-95defa57bb51</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>TOF</t>
+          <t>NEC</t>
         </is>
       </c>
     </row>
@@ -5103,12 +5103,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>CongDth</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Necrotising Enterocolitis (NEC)</t>
+          <t>Congenital Abnormality incompatible with life</t>
         </is>
       </c>
       <c r="D58">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>470b83f0-119e-4d3a-b4ea-95defa57bb51</t>
+          <t>324f84c3-45e1-4b21-be6a-e7480b611ac1</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>CongDth</t>
         </is>
       </c>
     </row>
@@ -5133,12 +5133,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>CongDth</t>
+          <t>Hypg</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Congenital Abnormality incompatible with life</t>
+          <t>Hypoglycaemia</t>
         </is>
       </c>
       <c r="D59">
@@ -5146,12 +5146,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>324f84c3-45e1-4b21-be6a-e7480b611ac1</t>
+          <t>2d5cb621-68a4-4c52-84d4-0da326bf72c1</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>CongDth</t>
+          <t>Hypg</t>
         </is>
       </c>
     </row>
@@ -5163,12 +5163,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Hypg</t>
+          <t>Hypo</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Hypoglycaemia</t>
+          <t>Hypothermia</t>
         </is>
       </c>
       <c r="D60">
@@ -5176,12 +5176,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2d5cb621-68a4-4c52-84d4-0da326bf72c1</t>
+          <t>d87c426f-1ab8-497b-ae5c-d91b2573ac16</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Hypg</t>
+          <t>Hypo</t>
         </is>
       </c>
     </row>
@@ -5193,12 +5193,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Hypo</t>
+          <t>EONS</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Hypothermia</t>
+          <t>Neonatal Sepsis - Early Onset (EONS)</t>
         </is>
       </c>
       <c r="D61">
@@ -5206,12 +5206,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>d87c426f-1ab8-497b-ae5c-d91b2573ac16</t>
+          <t>5afffeda-8bdb-4496-a48d-de45d9703a5c</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Hypo</t>
+          <t>EONS</t>
         </is>
       </c>
     </row>
@@ -5223,12 +5223,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>EONS</t>
+          <t>LONS</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Neonatal Sepsis - Early Onset (EONS)</t>
+          <t>Neonatal Sepsis - Late Onset (LONS)</t>
         </is>
       </c>
       <c r="D62">
@@ -5236,12 +5236,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>5afffeda-8bdb-4496-a48d-de45d9703a5c</t>
+          <t>2090fdeb-89f7-4614-a428-46ef56f1a5f7</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>EONS</t>
+          <t>LONS</t>
         </is>
       </c>
     </row>
@@ -5253,12 +5253,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>LONS</t>
+          <t>DJEx</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Neonatal Sepsis - Late Onset (LONS)</t>
+          <t>Pathological jaundice (Exchange transfusion required)</t>
         </is>
       </c>
       <c r="D63">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2090fdeb-89f7-4614-a428-46ef56f1a5f7</t>
+          <t>0a5eddbf-c74b-4a97-bc77-af3bfdc18e7b</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>LONS</t>
+          <t>DJEx</t>
         </is>
       </c>
     </row>
@@ -5283,12 +5283,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>DJEx</t>
+          <t>DJPh</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Pathological jaundice (Exchange transfusion required)</t>
+          <t>Pathological jaundice (phototherapy range)</t>
         </is>
       </c>
       <c r="D64">
@@ -5296,12 +5296,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>0a5eddbf-c74b-4a97-bc77-af3bfdc18e7b</t>
+          <t>08191b22-46f7-4dff-9ea7-3bb76489a1d5</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>DJEx</t>
+          <t>DJPh</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>DJPh</t>
+          <t>Unk</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Pathological jaundice (phototherapy range)</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D65">
@@ -5326,42 +5326,42 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>08191b22-46f7-4dff-9ea7-3bb76489a1d5</t>
+          <t>786afecb-ece6-43c3-9290-4d9f86f6a05d</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>DJPh</t>
+          <t>Unk</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>causedeath</t>
+          <t>causeofdeatknow</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>UNK</t>
+          <t>True</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D66">
-        <v>59</v>
+        <v>1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>786afecb-ece6-43c3-9290-4d9f86f6a05d</t>
+          <t>e36cf42e-6e0a-4b8e-8ccc-a0a1bda891e6</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>UNK</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -5373,55 +5373,55 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D67">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>e36cf42e-6e0a-4b8e-8ccc-a0a1bda891e6</t>
+          <t>2125e771-e059-492c-aec3-49cad8469b1c</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>causeofdeatknow</t>
+          <t>currcond</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>AlivWell</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Alive &amp; Well (Home)</t>
         </is>
       </c>
       <c r="D68">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2125e771-e059-492c-aec3-49cad8469b1c</t>
+          <t>daeb9cc9-dc8f-4e5a-9368-c568ef316165</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>AlivWell</t>
         </is>
       </c>
     </row>
@@ -5433,25 +5433,25 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>AlivWell</t>
+          <t>AlivNotWell</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Alive &amp; Well (Home)</t>
+          <t>Alive &amp; Not Well (Home)</t>
         </is>
       </c>
       <c r="D69">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>daeb9cc9-dc8f-4e5a-9368-c568ef316165</t>
+          <t>166e9c0d-4ae8-412f-b8ac-20de6677cf51</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>AlivWell</t>
+          <t>AlivNotWell</t>
         </is>
       </c>
     </row>
@@ -5463,25 +5463,25 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>AlivNotWell</t>
+          <t>AlivAdmi</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Alive &amp; Not Well (Home)</t>
+          <t>Alive &amp; Admitted</t>
         </is>
       </c>
       <c r="D70">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>166e9c0d-4ae8-412f-b8ac-20de6677cf51</t>
+          <t>e632b784-428a-4145-a03f-d6c707448972</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>AlivNotWell</t>
+          <t>AlivAdmi</t>
         </is>
       </c>
     </row>
@@ -5493,55 +5493,55 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>AlivAdmi</t>
+          <t>PassAway</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Alive &amp; Admitted</t>
+          <t>Passed Away</t>
         </is>
       </c>
       <c r="D71">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>e632b784-428a-4145-a03f-d6c707448972</t>
+          <t>c6863ec4-5c3b-4b61-a09e-fbb8b4e43f67</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>AlivAdmi</t>
+          <t>PassAway</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>currcond</t>
+          <t>day3chec</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>PassAway</t>
+          <t>True</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Passed Away</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D72">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>c6863ec4-5c3b-4b61-a09e-fbb8b4e43f67</t>
+          <t>e36cf42e-6e0a-4b8e-8ccc-a0a1bda891e6</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>PassAway</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -5553,55 +5553,55 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D73">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>e36cf42e-6e0a-4b8e-8ccc-a0a1bda891e6</t>
+          <t>2125e771-e059-492c-aec3-49cad8469b1c</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>day3chec</t>
+          <t>day7chec</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D74">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2125e771-e059-492c-aec3-49cad8469b1c</t>
+          <t>e36cf42e-6e0a-4b8e-8ccc-a0a1bda891e6</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -5613,55 +5613,55 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D75">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>e36cf42e-6e0a-4b8e-8ccc-a0a1bda891e6</t>
+          <t>2125e771-e059-492c-aec3-49cad8469b1c</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>day7chec</t>
+          <t>day7weigknow</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes I Know</t>
         </is>
       </c>
       <c r="D76">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2125e771-e059-492c-aec3-49cad8469b1c</t>
+          <t>e80d492c-255c-482c-b48a-c92f7e5939eb</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Y</t>
         </is>
       </c>
     </row>
@@ -5673,25 +5673,25 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>NS</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Yes I Know</t>
+          <t>Not Sure But Can Estimate</t>
         </is>
       </c>
       <c r="D77">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>e80d492c-255c-482c-b48a-c92f7e5939eb</t>
+          <t>1de45461-94fb-4557-84d8-58013a5de7fb</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>NS</t>
         </is>
       </c>
     </row>
@@ -5703,55 +5703,55 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>NS</t>
+          <t>N</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Not Sure But Can Estimate</t>
+          <t>No I Don't</t>
         </is>
       </c>
       <c r="D78">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>1de45461-94fb-4557-84d8-58013a5de7fb</t>
+          <t>80fa0e40-ea2c-4315-9002-97a0f3c617a4</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>NS</t>
+          <t>N</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>day7weigknow</t>
+          <t>feedasse</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Form</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>No I Don't</t>
+          <t>Formula</t>
         </is>
       </c>
       <c r="D79">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>80fa0e40-ea2c-4315-9002-97a0f3c617a4</t>
+          <t>66a478e5-3eb4-4bd7-afef-33d314af60b8</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Form</t>
         </is>
       </c>
     </row>
@@ -5763,25 +5763,25 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Form</t>
+          <t>BresMilk</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Formula</t>
+          <t>Breast Milk</t>
         </is>
       </c>
       <c r="D80">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>66a478e5-3eb4-4bd7-afef-33d314af60b8</t>
+          <t>39a6c447-5acf-44b5-b356-00ec91d4c888</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Form</t>
+          <t>BresMilk</t>
         </is>
       </c>
     </row>
@@ -5793,25 +5793,25 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>BresMilk</t>
+          <t>Wate</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Breast Milk</t>
+          <t>Water</t>
         </is>
       </c>
       <c r="D81">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>39a6c447-5acf-44b5-b356-00ec91d4c888</t>
+          <t>e81ea04e-384e-47fe-832b-83fee5a7286e</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>BresMilk</t>
+          <t>Wate</t>
         </is>
       </c>
     </row>
@@ -5823,25 +5823,25 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Wate</t>
+          <t>CookOil</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Water</t>
+          <t>Cooking Oil</t>
         </is>
       </c>
       <c r="D82">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>e81ea04e-384e-47fe-832b-83fee5a7286e</t>
+          <t>502b356f-7c49-43c5-ac03-4bef49625d37</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Wate</t>
+          <t>CookOil</t>
         </is>
       </c>
     </row>
@@ -5853,55 +5853,55 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>CookOil</t>
+          <t>SoliPorr</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Cooking Oil</t>
+          <t>Solids/ Porridge</t>
         </is>
       </c>
       <c r="D83">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>502b356f-7c49-43c5-ac03-4bef49625d37</t>
+          <t>f8345afd-0436-471b-8484-33d36961e448</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>CookOil</t>
+          <t>SoliPorr</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>feedasse</t>
+          <t>hosp</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>SoliPorr</t>
+          <t>True</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Solids/ Porridge</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D84">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>f8345afd-0436-471b-8484-33d36961e448</t>
+          <t>e36cf42e-6e0a-4b8e-8ccc-a0a1bda891e6</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>SoliPorr</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -5913,55 +5913,55 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D85">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>e36cf42e-6e0a-4b8e-8ccc-a0a1bda891e6</t>
+          <t>2125e771-e059-492c-aec3-49cad8469b1c</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>hosp</t>
+          <t>medigive</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D86">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2125e771-e059-492c-aec3-49cad8469b1c</t>
+          <t>e36cf42e-6e0a-4b8e-8ccc-a0a1bda891e6</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -5973,55 +5973,55 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D87">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>e36cf42e-6e0a-4b8e-8ccc-a0a1bda891e6</t>
+          <t>2125e771-e059-492c-aec3-49cad8469b1c</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>medigive</t>
+          <t>medihelp</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D88">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2125e771-e059-492c-aec3-49cad8469b1c</t>
+          <t>e36cf42e-6e0a-4b8e-8ccc-a0a1bda891e6</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -6033,55 +6033,55 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D89">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>e36cf42e-6e0a-4b8e-8ccc-a0a1bda891e6</t>
+          <t>2125e771-e059-492c-aec3-49cad8469b1c</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>medihelp</t>
+          <t>medihelptype</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>TradReli</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Traditional/Religious Help</t>
         </is>
       </c>
       <c r="D90">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2125e771-e059-492c-aec3-49cad8469b1c</t>
+          <t>430b2b91-f7e0-47ed-b444-8fd0e3f9f283</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>TradReli</t>
         </is>
       </c>
     </row>
@@ -6093,25 +6093,25 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>TradReli</t>
+          <t>PolyHosp</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Traditional/Religious Help</t>
+          <t>Polyclinic/Hospital</t>
         </is>
       </c>
       <c r="D91">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>430b2b91-f7e0-47ed-b444-8fd0e3f9f283</t>
+          <t>a6e85b5e-53ab-4afd-ad9c-8ac897231ec6</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>TradReli</t>
+          <t>PolyHosp</t>
         </is>
       </c>
     </row>
@@ -6123,25 +6123,25 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>PolyHosp</t>
+          <t>Pharm</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Polyclinic/Hospital</t>
+          <t>Pharmacy</t>
         </is>
       </c>
       <c r="D92">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>a6e85b5e-53ab-4afd-ad9c-8ac897231ec6</t>
+          <t>3785086d-236b-4c9f-8841-e43e0089a1aa</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>PolyHosp</t>
+          <t>Pharm</t>
         </is>
       </c>
     </row>
@@ -6153,25 +6153,25 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Pharm</t>
+          <t>TradReli</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Pharmacy</t>
+          <t>Traditional/ Religious Help</t>
         </is>
       </c>
       <c r="D93">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>3785086d-236b-4c9f-8841-e43e0089a1aa</t>
+          <t>63fec619-c10b-42e8-8004-a5e4157b0126</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Pharm</t>
+          <t>TradReli</t>
         </is>
       </c>
     </row>
@@ -6183,55 +6183,55 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>TradReli</t>
+          <t>PolyHosp</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Traditional/ Religious Help</t>
+          <t>Polyclinic/ Hospital</t>
         </is>
       </c>
       <c r="D94">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>63fec619-c10b-42e8-8004-a5e4157b0126</t>
+          <t>3584cb97-18dc-4dd5-b4c6-6981a1a5c7e9</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>TradReli</t>
+          <t>PolyHosp</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>medihelptype</t>
+          <t>neotreeoutcome</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>PolyHosp</t>
+          <t>DC</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Polyclinic/ Hospital</t>
+          <t>Discharged</t>
         </is>
       </c>
       <c r="D95">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>3584cb97-18dc-4dd5-b4c6-6981a1a5c7e9</t>
+          <t>43649e79-b816-4cf5-a986-11e6fca92744</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>PolyHosp</t>
+          <t>DC</t>
         </is>
       </c>
     </row>
@@ -6243,25 +6243,25 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>DC</t>
+          <t>NND&lt;24</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Discharged</t>
+          <t>Death (at LESS than 24 hrs of age)</t>
         </is>
       </c>
       <c r="D96">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>43649e79-b816-4cf5-a986-11e6fca92744</t>
+          <t>7e704490-b9de-4a10-be6b-0d9662619e41</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>DC</t>
+          <t>NND&lt;24</t>
         </is>
       </c>
     </row>
@@ -6273,25 +6273,25 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>NND&lt;24</t>
+          <t>NND&gt;24</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Death (at LESS than 24 hrs of age)</t>
+          <t>Death (at MORE than 24 hrs of age)</t>
         </is>
       </c>
       <c r="D97">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>7e704490-b9de-4a10-be6b-0d9662619e41</t>
+          <t>f1c27f9e-f324-44ff-b8a1-9dcc6e9e978c</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>NND&lt;24</t>
+          <t>NND&gt;24</t>
         </is>
       </c>
     </row>
@@ -6303,25 +6303,25 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>NND&gt;24</t>
+          <t>DDA</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Death (at MORE than 24 hrs of age)</t>
+          <t>Died during admission</t>
         </is>
       </c>
       <c r="D98">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>f1c27f9e-f324-44ff-b8a1-9dcc6e9e978c</t>
+          <t>b361d43a-3fc4-4384-9c99-162e09d3d297</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>NND&gt;24</t>
+          <t>DDA</t>
         </is>
       </c>
     </row>
@@ -6333,25 +6333,25 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>DDA</t>
+          <t>ABS</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Died During Admission</t>
+          <t>Absconded</t>
         </is>
       </c>
       <c r="D99">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>b361d43a-3fc4-4384-9c99-162e09d3d297</t>
+          <t>e4a6c032-322d-415a-82d2-6be63f9ba078</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>DDA</t>
+          <t>ABS</t>
         </is>
       </c>
     </row>
@@ -6363,25 +6363,25 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>ABS</t>
+          <t>TRO</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Absconded</t>
+          <t>Transferred to other ward</t>
         </is>
       </c>
       <c r="D100">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>e4a6c032-322d-415a-82d2-6be63f9ba078</t>
+          <t>35e526ce-3029-49a5-8690-47c25e03618f</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>ABS</t>
+          <t>TRO</t>
         </is>
       </c>
     </row>
@@ -6393,25 +6393,25 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>TRO</t>
+          <t>TRH</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Transferred to other ward</t>
+          <t>Transferred to other hospital</t>
         </is>
       </c>
       <c r="D101">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>35e526ce-3029-49a5-8690-47c25e03618f</t>
+          <t>10a66145-08f8-4a0e-81ee-e3aadccff87f</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>TRO</t>
+          <t>TRH</t>
         </is>
       </c>
     </row>
@@ -6423,25 +6423,25 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>TRH</t>
+          <t>DCR</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Transferred to other Hospital</t>
+          <t>Discharged on request</t>
         </is>
       </c>
       <c r="D102">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>10a66145-08f8-4a0e-81ee-e3aadccff87f</t>
+          <t>4037bf4f-28f3-4ab7-b9e2-29923173d2d3</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>TRH</t>
+          <t>DCR</t>
         </is>
       </c>
     </row>
@@ -6453,25 +6453,25 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>DCR</t>
+          <t>DPC</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Discharged on Request</t>
+          <t>Discharge on Palliative Care</t>
         </is>
       </c>
       <c r="D103">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>4037bf4f-28f3-4ab7-b9e2-29923173d2d3</t>
+          <t>3a8bd9e1-9c25-4702-abb8-699b081dd75d</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>DCR</t>
+          <t>DPC</t>
         </is>
       </c>
     </row>
@@ -6483,25 +6483,25 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>DPC</t>
+          <t>NND</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Discharge on Palliative Care</t>
+          <t>Died</t>
         </is>
       </c>
       <c r="D104">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>3a8bd9e1-9c25-4702-abb8-699b081dd75d</t>
+          <t>77e60ae9-6555-4cd4-9b42-0b63e6df782b</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>DPC</t>
+          <t>NND</t>
         </is>
       </c>
     </row>
@@ -6513,25 +6513,25 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>NND</t>
+          <t>BID</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Died</t>
+          <t>Brought in dead</t>
         </is>
       </c>
       <c r="D105">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>77e60ae9-6555-4cd4-9b42-0b63e6df782b</t>
+          <t>998e82df-e4a9-4b0d-9333-c08d4a64a18c</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>NND</t>
+          <t>BID</t>
         </is>
       </c>
     </row>
@@ -6543,25 +6543,25 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>BID</t>
+          <t>STB</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Brought in dead</t>
+          <t>Stillbirth</t>
         </is>
       </c>
       <c r="D106">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>998e82df-e4a9-4b0d-9333-c08d4a64a18c</t>
+          <t>09789e89-d117-4568-b61e-3f9240d3c684</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>BID</t>
+          <t>STB</t>
         </is>
       </c>
     </row>
@@ -6573,25 +6573,25 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>STB</t>
+          <t>DAMA</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Stillbirth</t>
+          <t>Discharged against medical advice</t>
         </is>
       </c>
       <c r="D107">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>09789e89-d117-4568-b61e-3f9240d3c684</t>
+          <t>754ba193-f6a8-4fe5-adb5-65c7e6ad4467</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>STB</t>
+          <t>DAMA</t>
         </is>
       </c>
     </row>
@@ -6603,25 +6603,25 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>DAMA</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Discharged against medical advice</t>
+          <t>Live Birth</t>
         </is>
       </c>
       <c r="D108">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>754ba193-f6a8-4fe5-adb5-65c7e6ad4467</t>
+          <t>e95c4c50-33e9-4e7b-9a43-704a5285225d</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>DAMA</t>
+          <t>LB</t>
         </is>
       </c>
     </row>
@@ -6633,25 +6633,25 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>ENND</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Live Birth</t>
+          <t>Early Neonatal Death</t>
         </is>
       </c>
       <c r="D109">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>e95c4c50-33e9-4e7b-9a43-704a5285225d</t>
+          <t>f5c87ec8-ddb3-4b9b-a7b0-515aa5f6c0ba</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>ENND</t>
         </is>
       </c>
     </row>
@@ -6663,25 +6663,25 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>ENND</t>
+          <t>STBM</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Early Neonatal Death</t>
+          <t>Stillbirth Macerated</t>
         </is>
       </c>
       <c r="D110">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>f5c87ec8-ddb3-4b9b-a7b0-515aa5f6c0ba</t>
+          <t>69c7a0e0-84f0-435c-8ef4-bc4ad88adbc3</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>ENND</t>
+          <t>STBM</t>
         </is>
       </c>
     </row>
@@ -6693,25 +6693,25 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>STBM</t>
+          <t>STBF</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Stillbirth Macerated</t>
+          <t>Stillbirth Fresh</t>
         </is>
       </c>
       <c r="D111">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>69c7a0e0-84f0-435c-8ef4-bc4ad88adbc3</t>
+          <t>393d3fad-3a61-4c1e-afe5-afff5c45e75c</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>STBM</t>
+          <t>STBF</t>
         </is>
       </c>
     </row>
@@ -6723,25 +6723,25 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>STBF</t>
+          <t>MISC</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Stillbirth Fresh</t>
+          <t>Miscarriage - born with no signs of life at under 22 weeks gestation</t>
         </is>
       </c>
       <c r="D112">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>393d3fad-3a61-4c1e-afe5-afff5c45e75c</t>
+          <t>d65ae47c-59a7-41c5-8c6c-f40c73fb6207</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>STBF</t>
+          <t>MISC</t>
         </is>
       </c>
     </row>
@@ -6753,25 +6753,25 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>MISC</t>
+          <t>STBM</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Miscarriage - born with no signs of life at under 22 weeks gestation</t>
+          <t>Stillbirth Mascerated</t>
         </is>
       </c>
       <c r="D113">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>d65ae47c-59a7-41c5-8c6c-f40c73fb6207</t>
+          <t>75d3d54b-e335-406a-96eb-565856a9d590</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>MISC</t>
+          <t>STBM</t>
         </is>
       </c>
     </row>
@@ -6783,25 +6783,25 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>STBM</t>
+          <t>MISC</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Stillbirth Mascerated</t>
+          <t>Miscarriage - death before 22 weeks' gestation</t>
         </is>
       </c>
       <c r="D114">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>75d3d54b-e335-406a-96eb-565856a9d590</t>
+          <t>87a75435-efd3-4127-a25a-5a115e69ef45</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>STBM</t>
+          <t>MISC</t>
         </is>
       </c>
     </row>
@@ -6813,55 +6813,55 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>MISC</t>
+          <t>TRO</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Miscarriage - death before 22 weeks' gestation</t>
+          <t>Transferred to another ward (example: paediatric ward)</t>
         </is>
       </c>
       <c r="D115">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>87a75435-efd3-4127-a25a-5a115e69ef45</t>
+          <t>509a9a6e-690a-4e06-8f57-8e37d2d4f3bd</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>MISC</t>
+          <t>TRO</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>neotreeoutcome</t>
+          <t>pretermclinatte</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>TRO</t>
+          <t>True</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Transferred to another ward (example: paediatric ward)</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D116">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>509a9a6e-690a-4e06-8f57-8e37d2d4f3bd</t>
+          <t>e36cf42e-6e0a-4b8e-8ccc-a0a1bda891e6</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>TRO</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -6873,55 +6873,55 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D117">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>e36cf42e-6e0a-4b8e-8ccc-a0a1bda891e6</t>
+          <t>2125e771-e059-492c-aec3-49cad8469b1c</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>pretermclinatte</t>
+          <t>reasquit</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not Comfortable to Say</t>
         </is>
       </c>
       <c r="D118">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>2125e771-e059-492c-aec3-49cad8469b1c</t>
+          <t>e0280383-61f0-4dc7-8c7c-6053c8d92885</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -6933,25 +6933,25 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Not Comfortable to Say</t>
+          <t>Open at Another Convenient Time</t>
         </is>
       </c>
       <c r="D119">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>e0280383-61f0-4dc7-8c7c-6053c8d92885</t>
+          <t>b3e04daa-d190-49a3-9514-3d1f2ce0b902</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -6963,55 +6963,55 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Open at Another Convenient Time</t>
+          <t>Other Reasons</t>
         </is>
       </c>
       <c r="D120">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>b3e04daa-d190-49a3-9514-3d1f2ce0b902</t>
+          <t>dd89c636-6b17-4a20-85af-fc76eb83500f</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>reasquit</t>
+          <t>receweigknow</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Other Reasons</t>
+          <t>Yes I Know</t>
         </is>
       </c>
       <c r="D121">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>dd89c636-6b17-4a20-85af-fc76eb83500f</t>
+          <t>e80d492c-255c-482c-b48a-c92f7e5939eb</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>Y</t>
         </is>
       </c>
     </row>
@@ -7023,25 +7023,25 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>NS</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Yes I Know</t>
+          <t>Not Sure But Can Estimate</t>
         </is>
       </c>
       <c r="D122">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>e80d492c-255c-482c-b48a-c92f7e5939eb</t>
+          <t>1de45461-94fb-4557-84d8-58013a5de7fb</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>NS</t>
         </is>
       </c>
     </row>
@@ -7053,55 +7053,55 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>NS</t>
+          <t>N</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Not Sure But Can Estimate</t>
+          <t>No I Don't</t>
         </is>
       </c>
       <c r="D123">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>1de45461-94fb-4557-84d8-58013a5de7fb</t>
+          <t>80fa0e40-ea2c-4315-9002-97a0f3c617a4</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>NS</t>
+          <t>N</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>receweigknow</t>
+          <t>termpre</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>True</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>No I Don't</t>
+          <t>Full Term</t>
         </is>
       </c>
       <c r="D124">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>80fa0e40-ea2c-4315-9002-97a0f3c617a4</t>
+          <t>139d02da-9ea9-43fc-97b5-a5b1d4bff017</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -7113,53 +7113,23 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Full Term</t>
+          <t>Pre-Term</t>
         </is>
       </c>
       <c r="D125">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>139d02da-9ea9-43fc-97b5-a5b1d4bff017</t>
+          <t>75be23d7-424e-4e56-91d2-804fc9333842</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>termpre</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>Pre-Term</t>
-        </is>
-      </c>
-      <c r="D126">
-        <v>2</v>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>75be23d7-424e-4e56-91d2-804fc9333842</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
         <is>
           <t>False</t>
         </is>
